--- a/data/chemical_requests.xlsx
+++ b/data/chemical_requests.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH10"/>
+  <dimension ref="A1:AH11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,11 +717,17 @@
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="n">
+        <v>46303.68806679398</v>
+      </c>
       <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="inlineStr"/>
@@ -841,12 +847,22 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>46303.68902793981</v>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>No good for this field, use LUMAX</t>
+        </is>
+      </c>
       <c r="AE3" t="inlineStr"/>
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="inlineStr"/>
@@ -965,11 +981,17 @@
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>46303.68939575231</v>
+      </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr"/>
       <c r="AF4" t="inlineStr"/>
@@ -1089,11 +1111,17 @@
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="n">
+        <v>46303.68985236111</v>
+      </c>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="inlineStr"/>
       <c r="AF5" t="inlineStr"/>
@@ -1455,11 +1483,17 @@
       <c r="Z8" t="inlineStr"/>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>46303.68964916667</v>
+      </c>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
@@ -1583,11 +1617,17 @@
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>46303.68951461805</v>
+      </c>
       <c r="AD9" t="inlineStr"/>
       <c r="AE9" t="inlineStr"/>
       <c r="AF9" t="inlineStr"/>
@@ -1601,7 +1641,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>46302.59941900846</v>
+        <v>46302.59941900463</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1711,17 +1751,151 @@
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>psibale</t>
+        </is>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>46303.68779935185</v>
+      </c>
       <c r="AD10" t="inlineStr"/>
       <c r="AE10" t="inlineStr"/>
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="inlineStr"/>
       <c r="AH10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>CR-2026-27-0010</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>46305.4474009802</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PROGRAMME</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>HERBICIDE</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Agriculture</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>admin</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>DG05004</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>HP070</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Irrigated</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Pre-Emergent</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Ametryn + Dual Magnum + MCPA</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Ametryn + Dual Magnum + MCPA</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2.0 + 2.0 + 2.0</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>L/ha + L/ha + L/ha</t>
+        </is>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>6.0 + 6.0 + 6.0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>L/ha + L/ha + L/ha</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>6.0 + 6.0 + 6.0</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="W11" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Planned herbicide programme</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
